--- a/planning/uat/round-0/fixtures-data/elec-30.xlsx
+++ b/planning/uat/round-0/fixtures-data/elec-30.xlsx
@@ -30,7 +30,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 1</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -47,7 +47,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 2</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -64,7 +64,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 3</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -81,7 +81,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 4</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -98,7 +98,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 5</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -115,7 +115,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 6</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -132,7 +132,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 7</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -149,7 +149,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 8</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -166,7 +166,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 9</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -183,7 +183,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 10</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -200,7 +200,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 11</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -217,7 +217,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 12</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -234,7 +234,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 13</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -251,7 +251,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 14</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -268,7 +268,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 15</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 16</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -302,7 +302,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 17</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -319,7 +319,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 18</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -336,7 +336,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 19</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -353,7 +353,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 20</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -370,7 +370,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 21</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -387,7 +387,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 22</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 23</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 24</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -438,7 +438,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 25</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 26</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -472,7 +472,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 27</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 28</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 29</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-09 184405 item 30</t>
+          <t xml:space="preserve">UAT IMP-09 190749 item 30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
